--- a/clients/encore/testcases/create-new-product-groups/item-search-create-new-product-groups.xlsx
+++ b/clients/encore/testcases/create-new-product-groups/item-search-create-new-product-groups.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="237">
   <si>
     <t>TC ID</t>
   </si>
@@ -177,13 +177,13 @@
     <t>3. In the sub-class picker, double-click one item in the left list</t>
   </si>
   <si>
-    <t>The item moves to the Sub Classes area on the right, and — with Name, Description, Service Type and one sub-class all set — Save enables</t>
+    <t>The item appears in the Sub Classes area on the right (and stays in the left list), and — with Name, Description, Service Type and one sub-class all set — Save enables</t>
   </si>
   <si>
     <t>4. Click Save</t>
   </si>
   <si>
-    <t>A "Product Group created successfully" toast appears and the page redirects to the groups list; `POST /navigator/api/location/add-update-product-group` returns 200</t>
+    <t>A "Product Group created successfully" toast appears and the page lands on the groups list (its address ends in `/products/product-groups`); `POST /navigator/api/location/add-update-product-group` returns 200</t>
   </si>
   <si>
     <t>5. Search the groups list for the new group's exact Name</t>
@@ -192,19 +192,558 @@
     <t>Exactly one row returns — the group just created, showing its Description and Service Type</t>
   </si>
   <si>
+    <t>TC-ISR-PGR-012</t>
+  </si>
+  <si>
+    <t>Name accepts exactly 50 characters and drops the rest silently</t>
+  </si>
+  <si>
+    <t>The Add page is open with an empty form</t>
+  </si>
+  <si>
+    <t>1. Type 50 characters into Name, one key at a time</t>
+  </si>
+  <si>
+    <t>The box holds all 50</t>
+  </si>
+  <si>
+    <t>2. Type one more character</t>
+  </si>
+  <si>
+    <t>The box still holds 50 — the 51st is dropped; no message appears and the box is not marked invalid</t>
+  </si>
+  <si>
+    <t>3. Select all and paste a 60-character value</t>
+  </si>
+  <si>
+    <t>The box holds exactly the first 50</t>
+  </si>
+  <si>
+    <t>4. Press Tab</t>
+  </si>
+  <si>
+    <t>Focus leaves the box normally</t>
+  </si>
+  <si>
+    <t>5. Click Cancel</t>
+  </si>
+  <si>
+    <t>The list page returns; nothing was saved</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-013</t>
+  </si>
+  <si>
+    <t>Description accepts exactly 100 characters and drops the rest silently</t>
+  </si>
+  <si>
+    <t>1. Paste a 120-character value into Description</t>
+  </si>
+  <si>
+    <t>The box holds exactly the first 100</t>
+  </si>
+  <si>
+    <t>2. Press End and type one more character</t>
+  </si>
+  <si>
+    <t>The box still holds 100</t>
+  </si>
+  <si>
+    <t>3. Press Tab</t>
+  </si>
+  <si>
+    <t>4. Click Cancel</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-014</t>
+  </si>
+  <si>
+    <t>Clearing a filled Name by either method holds Save back and marks the box invalid</t>
+  </si>
+  <si>
+    <t>The Add page is open with Name, Description, a Service Type and one sub-class set, so Save is enabled</t>
+  </si>
+  <si>
+    <t>1. Click into Name, select all and press Delete</t>
+  </si>
+  <si>
+    <t>The box is empty, shows a red border and is marked invalid; Save is disabled</t>
+  </si>
+  <si>
+    <t>2. Press Tab</t>
+  </si>
+  <si>
+    <t>Focus leaves the box — the invalid state does not trap it</t>
+  </si>
+  <si>
+    <t>3. Type the name again</t>
+  </si>
+  <si>
+    <t>The invalid mark clears and Save enables</t>
+  </si>
+  <si>
+    <t>4. Press Backspace once per character until the box is empty</t>
+  </si>
+  <si>
+    <t>The same invalid state; Save is disabled</t>
+  </si>
+  <si>
+    <t>5. Type the name again</t>
+  </si>
+  <si>
+    <t>Save enables</t>
+  </si>
+  <si>
+    <t>6. Click Cancel</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-015</t>
+  </si>
+  <si>
+    <t>A whitespace-only Name counts as empty; a padded Name is accepted</t>
+  </si>
+  <si>
+    <t>The Add page is open with Description, a Service Type and one sub-class set</t>
+  </si>
+  <si>
+    <t>1. Fill Name with spaces only</t>
+  </si>
+  <si>
+    <t>The box is marked invalid and Save stays disabled</t>
+  </si>
+  <si>
+    <t>2. Fill Name with a value surrounded by spaces</t>
+  </si>
+  <si>
+    <t>The box is not marked invalid and Save enables</t>
+  </si>
+  <si>
+    <t>3. Click Cancel</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-016</t>
+  </si>
+  <si>
+    <t>Every required field gates Save, and Active does not</t>
+  </si>
+  <si>
+    <t>1. Fill Name and Description and choose a Service Type</t>
+  </si>
+  <si>
+    <t>Save is still disabled — no sub-class yet</t>
+  </si>
+  <si>
+    <t>2. Double-click one catalog item</t>
+  </si>
+  <si>
+    <t>3. Clear Description</t>
+  </si>
+  <si>
+    <t>Save is disabled</t>
+  </si>
+  <si>
+    <t>4. Refill Description</t>
+  </si>
+  <si>
+    <t>5. Remove the added sub-class with its x control</t>
+  </si>
+  <si>
+    <t>The instruction text returns and Save is disabled</t>
+  </si>
+  <si>
+    <t>6. Double-click a catalog item again</t>
+  </si>
+  <si>
+    <t>7. Clear Active, then check it again</t>
+  </si>
+  <si>
+    <t>Save stays enabled both times</t>
+  </si>
+  <si>
+    <t>8. Click Cancel</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-017</t>
+  </si>
+  <si>
+    <t>The Service Type list offers its 90 options with no search box, and first, middle and last all select</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator
+Sample input 1: "Lighting"</t>
+  </si>
+  <si>
+    <t>1. Open the Service Type list</t>
+  </si>
+  <si>
+    <t>It opens with exactly the 90 options recorded in the inventory, in that order, starting with "Equipment Rental" and ending with "ZSub Rental Specialty"; there is no search box inside the list</t>
+  </si>
+  <si>
+    <t>2. Choose the first option</t>
+  </si>
+  <si>
+    <t>The selector shows "Equipment Rental"</t>
+  </si>
+  <si>
+    <t>3. Open the list, press End, press Enter</t>
+  </si>
+  <si>
+    <t>The selector shows "ZSub Rental Specialty"</t>
+  </si>
+  <si>
+    <t>4. Open the list and click a middle option ("Lighting")</t>
+  </si>
+  <si>
+    <t>The selector shows "Lighting"</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-018</t>
+  </si>
+  <si>
+    <t>A name already used by another group is rejected, with or without a trailing space</t>
+  </si>
+  <si>
+    <t>The Add page is open. The fixture group ZZ E2E Walk 2026-09-09 A (description walk probe A) exists on office 1101</t>
+  </si>
+  <si>
+    <t>1. Fill Name with the fixture group's name, a fresh Description, a Service Type and one sub-class</t>
+  </si>
+  <si>
+    <t>2. Click Save</t>
+  </si>
+  <si>
+    <t>An error toast reads `Product group name 'ZZ E2E Walk 2026-09-09 A' or group description '&lt;the fresh description&gt;' already exists.`; the page stays on the Add form with every value kept; Save is still enabled</t>
+  </si>
+  <si>
+    <t>3. Change Name to the same name with a trailing space and click Save</t>
+  </si>
+  <si>
+    <t>The same error toast, showing the name without the trailing space — the server trims before comparing</t>
+  </si>
+  <si>
+    <t>The list page returns; nothing was created</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-019</t>
+  </si>
+  <si>
+    <t>A description already used by another group is rejected even with a new name</t>
+  </si>
+  <si>
+    <t>1. Fill Name with a per-run unique value, Description with the fixture group's description, a Service Type and one sub-class</t>
+  </si>
+  <si>
+    <t>An error toast reads `Product group name '&lt;the new name&gt;' or group description 'walk probe A' already exists.`; the page stays on the Add form; Save is still enabled</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-020</t>
+  </si>
+  <si>
+    <t>The picker search filters the catalog by substring regardless of case and empties on no match</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator
+Sample input 1: "Scenery"
+Sample input 2: "SCENERY"</t>
+  </si>
+  <si>
+    <t>1. Read the catalog row count</t>
+  </si>
+  <si>
+    <t>A positive count — the full catalog, read live rather than assumed (several thousand rows)</t>
+  </si>
+  <si>
+    <t>2. Type "Scenery" into the picker's Search</t>
+  </si>
+  <si>
+    <t>Fewer rows than step 1, and every remaining row contains "Scenery"</t>
+  </si>
+  <si>
+    <t>3. Replace it with "SCENERY"</t>
+  </si>
+  <si>
+    <t>The same number of rows as step 2</t>
+  </si>
+  <si>
+    <t>4. Replace it with a value that matches nothing</t>
+  </si>
+  <si>
+    <t>Zero rows</t>
+  </si>
+  <si>
+    <t>5. Clear the Search box</t>
+  </si>
+  <si>
+    <t>The count from step 1 returns</t>
+  </si>
+  <si>
+    <t>The list page returns</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-021</t>
+  </si>
+  <si>
+    <t>The Labor filter narrows the catalog and unchecking restores it</t>
+  </si>
+  <si>
+    <t>1. Read the catalog row count and first row</t>
+  </si>
+  <si>
+    <t>The full catalog</t>
+  </si>
+  <si>
+    <t>2. Check Labor</t>
+  </si>
+  <si>
+    <t>Fewer rows than step 1 (a few hundred labor sub-classes), and the first row is a different item</t>
+  </si>
+  <si>
+    <t>3. Uncheck Labor</t>
+  </si>
+  <si>
+    <t>The count and first row from step 1 return</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-022</t>
+  </si>
+  <si>
+    <t>Sort order flips the catalog between ascending and descending</t>
+  </si>
+  <si>
+    <t>1. Read the first and last catalog rows with the order at Ascending</t>
+  </si>
+  <si>
+    <t>Two different items</t>
+  </si>
+  <si>
+    <t>2. Choose Descending</t>
+  </si>
+  <si>
+    <t>The first row is step 1's last row and the last row is step 1's first row</t>
+  </si>
+  <si>
+    <t>3. Choose Ascending</t>
+  </si>
+  <si>
+    <t>Step 1's first and last rows return</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-023</t>
+  </si>
+  <si>
+    <t>Reset clears the picker's search, filter and sort but keeps an added sub-class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator
+Sample input 1: "Scenery"</t>
+  </si>
+  <si>
+    <t>1. Double-click one catalog item</t>
+  </si>
+  <si>
+    <t>It appears in the Sub Classes area</t>
+  </si>
+  <si>
+    <t>2. Type "Scenery" into Search, check Labor, choose Descending</t>
+  </si>
+  <si>
+    <t>Search holds "Scenery", Labor is checked, the order shows Descending, and the three filters compose as one (the catalog holds no labor scenery, so the list may well be empty)</t>
+  </si>
+  <si>
+    <t>3. Click Reset</t>
+  </si>
+  <si>
+    <t>Search is empty, Labor is unchecked, the order shows Ascending, the full catalog is back — and the sub-class added in step 1 is still in the Sub Classes area</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-024</t>
+  </si>
+  <si>
+    <t>Double-click adds an item once and the x control removes it</t>
+  </si>
+  <si>
+    <t>1. Double-click the first catalog item</t>
+  </si>
+  <si>
+    <t>It appears once in the Sub Classes area; the instruction text is gone; the catalog still lists it</t>
+  </si>
+  <si>
+    <t>2. Double-click the same item again</t>
+  </si>
+  <si>
+    <t>The Sub Classes area still shows it once</t>
+  </si>
+  <si>
+    <t>3. Click the x on the added row</t>
+  </si>
+  <si>
+    <t>The Sub Classes area is empty and the instruction text is back; the catalog is unchanged</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-025</t>
+  </si>
+  <si>
+    <t>Dragging an item onto the Sub Classes area adds it</t>
+  </si>
+  <si>
+    <t>The Add page is open with no sub-class added</t>
+  </si>
+  <si>
+    <t>1. Press the mouse on a catalog item, move it in steps onto the Sub Classes area, release</t>
+  </si>
+  <si>
+    <t>The item appears in the Sub Classes area and the instruction text is gone</t>
+  </si>
+  <si>
+    <t>2. Click Cancel</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-026</t>
+  </si>
+  <si>
+    <t>The divider button collapses and expands the sub-class panel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator
+Sample input 1: "Collapse search panel"
+Sample input 2: "Expand search panel"</t>
+  </si>
+  <si>
+    <t>1. Read the Name box's left edge and width</t>
+  </si>
+  <si>
+    <t>Values with the panel shown</t>
+  </si>
+  <si>
+    <t>2. Click the "Collapse search panel" button</t>
+  </si>
+  <si>
+    <t>The button now reads "Expand search panel"; the Name box starts further left and is wider than in step 1 — the form has taken the panel's room</t>
+  </si>
+  <si>
+    <t>3. Click the "Expand search panel" button</t>
+  </si>
+  <si>
+    <t>The button reads "Collapse search panel" again and the Name box has step 1's left edge and width</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-027</t>
+  </si>
+  <si>
+    <t>A group saved with Active cleared is created inactive and found with the list's Active filter cleared</t>
+  </si>
+  <si>
+    <t>Save is enabled</t>
+  </si>
+  <si>
+    <t>2. fill a per-run unique Name and Description, choose a Service Type, add one sub-class by double-click, and clear Active</t>
+  </si>
+  <si>
+    <t>The "Product Group created successfully" toast appears and the page lands on the groups list</t>
+  </si>
+  <si>
+    <t>3. Click Save</t>
+  </si>
+  <si>
+    <t>4. Search the list for the new name with the Active filter checked</t>
+  </si>
+  <si>
+    <t>Exactly one row — the new group, with Status "Inactive"</t>
+  </si>
+  <si>
+    <t>5. Clear the Active filter and search again</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-028</t>
+  </si>
+  <si>
+    <t>Special characters in the name are stored verbatim and the last Service Type saves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator
+Sample input 1: "&lt;/b&gt;, a Description, choose "</t>
+  </si>
+  <si>
+    <t>2. fill Name with a per-run unique value containing &lt;b&gt;&amp;'"&lt;/b&gt;, a Description, choose "ZSub Rental Specialty" (the last option) and add one sub-class</t>
+  </si>
+  <si>
+    <t>The success toast appears and the page lands on the groups list</t>
+  </si>
+  <si>
+    <t>Exactly one row — Name shown exactly as typed, tags and quotes included, as plain text; Service Type "ZSub Rental Specialty"; Status "Active"</t>
+  </si>
+  <si>
+    <t>4. Search the list for the new group</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-029</t>
+  </si>
+  <si>
+    <t>Browser Back leaves the Add page without saving or warning</t>
+  </si>
+  <si>
+    <t>The Add page is open, reached from the list page</t>
+  </si>
+  <si>
+    <t>1. Type a value into Name</t>
+  </si>
+  <si>
+    <t>The box holds it</t>
+  </si>
+  <si>
+    <t>2. Go back in the browser history</t>
+  </si>
+  <si>
+    <t>The list page returns with no warning prompt</t>
+  </si>
+  <si>
+    <t>3. Click Add</t>
+  </si>
+  <si>
+    <t>The form is empty; nothing was kept</t>
+  </si>
+  <si>
+    <t>TC-ISR-PGR-030</t>
+  </si>
+  <si>
+    <t>The breadcrumb leaves the Add page without saving or warning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator
+Sample input 1: "Product Groups"</t>
+  </si>
+  <si>
+    <t>2. Click the "Product Groups" breadcrumb above the form</t>
+  </si>
+  <si>
+    <t>The list page opens with no warning prompt</t>
+  </si>
+  <si>
     <t>SUMMARY</t>
   </si>
   <si>
     <t>Item Search — Create new Product Groups</t>
   </si>
   <si>
-    <t>Automated: 4 / Pending: 0</t>
-  </si>
-  <si>
-    <t>Pass:4 Fail:0 Skipped:0 Blocked:0</t>
-  </si>
-  <si>
-    <t>Last Updated: 2026-09-08</t>
+    <t>Automated: 23 / Pending: 0</t>
+  </si>
+  <si>
+    <t>Pass:23 Fail:0 Skipped:0 Blocked:0</t>
+  </si>
+  <si>
+    <t>Last Updated: 2026-09-09</t>
   </si>
 </sst>
 </file>
@@ -593,19 +1132,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M97"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="70" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="80" customWidth="1"/>
     <col min="6" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="27" customWidth="1"/>
-    <col min="9" max="9" width="35" customWidth="1"/>
-    <col min="10" max="10" width="55" customWidth="1"/>
-    <col min="11" max="12" width="80" customWidth="1"/>
+    <col min="8" max="8" width="28" customWidth="1"/>
+    <col min="9" max="9" width="36" customWidth="1"/>
+    <col min="10" max="12" width="80" customWidth="1"/>
     <col min="13" max="13" width="26" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1183,45 +1721,3366 @@
         <v>25</v>
       </c>
     </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" t="s">
+        <v>20</v>
+      </c>
+      <c r="I15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" t="s">
+        <v>61</v>
+      </c>
+      <c r="K15" t="s">
+        <v>62</v>
+      </c>
+      <c r="L15" t="s">
+        <v>63</v>
+      </c>
+      <c r="M15" t="s">
+        <v>25</v>
+      </c>
+    </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H16" s="2" t="s">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" t="s">
+        <v>25</v>
+      </c>
+      <c r="I16" t="s">
+        <v>25</v>
+      </c>
+      <c r="J16" t="s">
+        <v>25</v>
+      </c>
+      <c r="K16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I17" t="s">
+        <v>25</v>
+      </c>
+      <c r="J17" t="s">
+        <v>25</v>
+      </c>
+      <c r="K17" t="s">
+        <v>66</v>
+      </c>
+      <c r="L17" t="s">
+        <v>67</v>
+      </c>
+      <c r="M17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" t="s">
+        <v>25</v>
+      </c>
+      <c r="I18" t="s">
+        <v>25</v>
+      </c>
+      <c r="J18" t="s">
+        <v>25</v>
+      </c>
+      <c r="K18" t="s">
+        <v>68</v>
+      </c>
+      <c r="L18" t="s">
+        <v>69</v>
+      </c>
+      <c r="M18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H19" t="s">
+        <v>25</v>
+      </c>
+      <c r="I19" t="s">
+        <v>25</v>
+      </c>
+      <c r="J19" t="s">
+        <v>25</v>
+      </c>
+      <c r="K19" t="s">
+        <v>70</v>
+      </c>
+      <c r="L19" t="s">
+        <v>71</v>
+      </c>
+      <c r="M19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" t="s">
+        <v>20</v>
+      </c>
+      <c r="I20" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" t="s">
         <v>61</v>
       </c>
-      <c r="I16" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>63</v>
+      <c r="K20" t="s">
+        <v>74</v>
+      </c>
+      <c r="L20" t="s">
+        <v>75</v>
+      </c>
+      <c r="M20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H21" t="s">
+        <v>25</v>
+      </c>
+      <c r="I21" t="s">
+        <v>25</v>
+      </c>
+      <c r="J21" t="s">
+        <v>25</v>
+      </c>
+      <c r="K21" t="s">
+        <v>76</v>
+      </c>
+      <c r="L21" t="s">
+        <v>77</v>
+      </c>
+      <c r="M21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" t="s">
+        <v>25</v>
+      </c>
+      <c r="G22" t="s">
+        <v>25</v>
+      </c>
+      <c r="H22" t="s">
+        <v>25</v>
+      </c>
+      <c r="I22" t="s">
+        <v>25</v>
+      </c>
+      <c r="J22" t="s">
+        <v>25</v>
+      </c>
+      <c r="K22" t="s">
+        <v>78</v>
+      </c>
+      <c r="L22" t="s">
+        <v>69</v>
+      </c>
+      <c r="M22" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" t="s">
+        <v>25</v>
+      </c>
+      <c r="G23" t="s">
+        <v>25</v>
+      </c>
+      <c r="H23" t="s">
+        <v>25</v>
+      </c>
+      <c r="I23" t="s">
+        <v>25</v>
+      </c>
+      <c r="J23" t="s">
+        <v>25</v>
+      </c>
+      <c r="K23" t="s">
+        <v>79</v>
+      </c>
+      <c r="L23" t="s">
+        <v>71</v>
+      </c>
+      <c r="M23" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" t="s">
+        <v>20</v>
+      </c>
+      <c r="I24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J24" t="s">
+        <v>82</v>
+      </c>
+      <c r="K24" t="s">
+        <v>83</v>
+      </c>
+      <c r="L24" t="s">
+        <v>84</v>
+      </c>
+      <c r="M24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" t="s">
+        <v>25</v>
+      </c>
+      <c r="G25" t="s">
+        <v>25</v>
+      </c>
+      <c r="H25" t="s">
+        <v>25</v>
+      </c>
+      <c r="I25" t="s">
+        <v>25</v>
+      </c>
+      <c r="J25" t="s">
+        <v>25</v>
+      </c>
+      <c r="K25" t="s">
+        <v>85</v>
+      </c>
+      <c r="L25" t="s">
+        <v>86</v>
+      </c>
+      <c r="M25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" t="s">
+        <v>25</v>
+      </c>
+      <c r="G26" t="s">
+        <v>25</v>
+      </c>
+      <c r="H26" t="s">
+        <v>25</v>
+      </c>
+      <c r="I26" t="s">
+        <v>25</v>
+      </c>
+      <c r="J26" t="s">
+        <v>25</v>
+      </c>
+      <c r="K26" t="s">
+        <v>87</v>
+      </c>
+      <c r="L26" t="s">
+        <v>88</v>
+      </c>
+      <c r="M26" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D27" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" t="s">
+        <v>25</v>
+      </c>
+      <c r="G27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H27" t="s">
+        <v>25</v>
+      </c>
+      <c r="I27" t="s">
+        <v>25</v>
+      </c>
+      <c r="J27" t="s">
+        <v>25</v>
+      </c>
+      <c r="K27" t="s">
+        <v>89</v>
+      </c>
+      <c r="L27" t="s">
+        <v>90</v>
+      </c>
+      <c r="M27" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" t="s">
+        <v>25</v>
+      </c>
+      <c r="E28" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" t="s">
+        <v>25</v>
+      </c>
+      <c r="G28" t="s">
+        <v>25</v>
+      </c>
+      <c r="H28" t="s">
+        <v>25</v>
+      </c>
+      <c r="I28" t="s">
+        <v>25</v>
+      </c>
+      <c r="J28" t="s">
+        <v>25</v>
+      </c>
+      <c r="K28" t="s">
+        <v>91</v>
+      </c>
+      <c r="L28" t="s">
+        <v>92</v>
+      </c>
+      <c r="M28" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29" t="s">
+        <v>25</v>
+      </c>
+      <c r="G29" t="s">
+        <v>25</v>
+      </c>
+      <c r="H29" t="s">
+        <v>25</v>
+      </c>
+      <c r="I29" t="s">
+        <v>25</v>
+      </c>
+      <c r="J29" t="s">
+        <v>25</v>
+      </c>
+      <c r="K29" t="s">
+        <v>93</v>
+      </c>
+      <c r="L29" t="s">
+        <v>71</v>
+      </c>
+      <c r="M29" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>94</v>
+      </c>
+      <c r="B30" t="s">
+        <v>95</v>
+      </c>
+      <c r="C30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" t="s">
+        <v>17</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" t="s">
+        <v>19</v>
+      </c>
+      <c r="H30" t="s">
+        <v>20</v>
+      </c>
+      <c r="I30" t="s">
+        <v>21</v>
+      </c>
+      <c r="J30" t="s">
+        <v>96</v>
+      </c>
+      <c r="K30" t="s">
+        <v>97</v>
+      </c>
+      <c r="L30" t="s">
+        <v>98</v>
+      </c>
+      <c r="M30" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" t="s">
+        <v>25</v>
+      </c>
+      <c r="G31" t="s">
+        <v>25</v>
+      </c>
+      <c r="H31" t="s">
+        <v>25</v>
+      </c>
+      <c r="I31" t="s">
+        <v>25</v>
+      </c>
+      <c r="J31" t="s">
+        <v>25</v>
+      </c>
+      <c r="K31" t="s">
+        <v>99</v>
+      </c>
+      <c r="L31" t="s">
+        <v>100</v>
+      </c>
+      <c r="M31" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" t="s">
+        <v>25</v>
+      </c>
+      <c r="D32" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" t="s">
+        <v>25</v>
+      </c>
+      <c r="G32" t="s">
+        <v>25</v>
+      </c>
+      <c r="H32" t="s">
+        <v>25</v>
+      </c>
+      <c r="I32" t="s">
+        <v>25</v>
+      </c>
+      <c r="J32" t="s">
+        <v>25</v>
+      </c>
+      <c r="K32" t="s">
+        <v>101</v>
+      </c>
+      <c r="L32" t="s">
+        <v>71</v>
+      </c>
+      <c r="M32" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>102</v>
+      </c>
+      <c r="B33" t="s">
+        <v>103</v>
+      </c>
+      <c r="C33" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" t="s">
+        <v>19</v>
+      </c>
+      <c r="H33" t="s">
+        <v>20</v>
+      </c>
+      <c r="I33" t="s">
+        <v>21</v>
+      </c>
+      <c r="J33" t="s">
+        <v>61</v>
+      </c>
+      <c r="K33" t="s">
+        <v>104</v>
+      </c>
+      <c r="L33" t="s">
+        <v>105</v>
+      </c>
+      <c r="M33" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" t="s">
+        <v>25</v>
+      </c>
+      <c r="D34" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" t="s">
+        <v>25</v>
+      </c>
+      <c r="F34" t="s">
+        <v>25</v>
+      </c>
+      <c r="G34" t="s">
+        <v>25</v>
+      </c>
+      <c r="H34" t="s">
+        <v>25</v>
+      </c>
+      <c r="I34" t="s">
+        <v>25</v>
+      </c>
+      <c r="J34" t="s">
+        <v>25</v>
+      </c>
+      <c r="K34" t="s">
+        <v>106</v>
+      </c>
+      <c r="L34" t="s">
+        <v>92</v>
+      </c>
+      <c r="M34" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" t="s">
+        <v>25</v>
+      </c>
+      <c r="D35" t="s">
+        <v>25</v>
+      </c>
+      <c r="E35" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35" t="s">
+        <v>25</v>
+      </c>
+      <c r="G35" t="s">
+        <v>25</v>
+      </c>
+      <c r="H35" t="s">
+        <v>25</v>
+      </c>
+      <c r="I35" t="s">
+        <v>25</v>
+      </c>
+      <c r="J35" t="s">
+        <v>25</v>
+      </c>
+      <c r="K35" t="s">
+        <v>107</v>
+      </c>
+      <c r="L35" t="s">
+        <v>108</v>
+      </c>
+      <c r="M35" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>25</v>
+      </c>
+      <c r="B36" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" t="s">
+        <v>25</v>
+      </c>
+      <c r="D36" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" t="s">
+        <v>25</v>
+      </c>
+      <c r="F36" t="s">
+        <v>25</v>
+      </c>
+      <c r="G36" t="s">
+        <v>25</v>
+      </c>
+      <c r="H36" t="s">
+        <v>25</v>
+      </c>
+      <c r="I36" t="s">
+        <v>25</v>
+      </c>
+      <c r="J36" t="s">
+        <v>25</v>
+      </c>
+      <c r="K36" t="s">
+        <v>109</v>
+      </c>
+      <c r="L36" t="s">
+        <v>92</v>
+      </c>
+      <c r="M36" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>25</v>
+      </c>
+      <c r="B37" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" t="s">
+        <v>25</v>
+      </c>
+      <c r="D37" t="s">
+        <v>25</v>
+      </c>
+      <c r="E37" t="s">
+        <v>25</v>
+      </c>
+      <c r="F37" t="s">
+        <v>25</v>
+      </c>
+      <c r="G37" t="s">
+        <v>25</v>
+      </c>
+      <c r="H37" t="s">
+        <v>25</v>
+      </c>
+      <c r="I37" t="s">
+        <v>25</v>
+      </c>
+      <c r="J37" t="s">
+        <v>25</v>
+      </c>
+      <c r="K37" t="s">
+        <v>110</v>
+      </c>
+      <c r="L37" t="s">
+        <v>111</v>
+      </c>
+      <c r="M37" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>25</v>
+      </c>
+      <c r="B38" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" t="s">
+        <v>25</v>
+      </c>
+      <c r="D38" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" t="s">
+        <v>25</v>
+      </c>
+      <c r="F38" t="s">
+        <v>25</v>
+      </c>
+      <c r="G38" t="s">
+        <v>25</v>
+      </c>
+      <c r="H38" t="s">
+        <v>25</v>
+      </c>
+      <c r="I38" t="s">
+        <v>25</v>
+      </c>
+      <c r="J38" t="s">
+        <v>25</v>
+      </c>
+      <c r="K38" t="s">
+        <v>112</v>
+      </c>
+      <c r="L38" t="s">
+        <v>92</v>
+      </c>
+      <c r="M38" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>25</v>
+      </c>
+      <c r="B39" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" t="s">
+        <v>25</v>
+      </c>
+      <c r="D39" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F39" t="s">
+        <v>25</v>
+      </c>
+      <c r="G39" t="s">
+        <v>25</v>
+      </c>
+      <c r="H39" t="s">
+        <v>25</v>
+      </c>
+      <c r="I39" t="s">
+        <v>25</v>
+      </c>
+      <c r="J39" t="s">
+        <v>25</v>
+      </c>
+      <c r="K39" t="s">
+        <v>113</v>
+      </c>
+      <c r="L39" t="s">
+        <v>114</v>
+      </c>
+      <c r="M39" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>25</v>
+      </c>
+      <c r="B40" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" t="s">
+        <v>25</v>
+      </c>
+      <c r="D40" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" t="s">
+        <v>25</v>
+      </c>
+      <c r="F40" t="s">
+        <v>25</v>
+      </c>
+      <c r="G40" t="s">
+        <v>25</v>
+      </c>
+      <c r="H40" t="s">
+        <v>25</v>
+      </c>
+      <c r="I40" t="s">
+        <v>25</v>
+      </c>
+      <c r="J40" t="s">
+        <v>25</v>
+      </c>
+      <c r="K40" t="s">
+        <v>115</v>
+      </c>
+      <c r="L40" t="s">
+        <v>71</v>
+      </c>
+      <c r="M40" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>116</v>
+      </c>
+      <c r="B41" t="s">
+        <v>117</v>
+      </c>
+      <c r="C41" t="s">
+        <v>15</v>
+      </c>
+      <c r="D41" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" t="s">
+        <v>118</v>
+      </c>
+      <c r="F41" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" t="s">
+        <v>19</v>
+      </c>
+      <c r="H41" t="s">
+        <v>20</v>
+      </c>
+      <c r="I41" t="s">
+        <v>21</v>
+      </c>
+      <c r="J41" t="s">
+        <v>61</v>
+      </c>
+      <c r="K41" t="s">
+        <v>119</v>
+      </c>
+      <c r="L41" t="s">
+        <v>120</v>
+      </c>
+      <c r="M41" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C42" t="s">
+        <v>25</v>
+      </c>
+      <c r="D42" t="s">
+        <v>25</v>
+      </c>
+      <c r="E42" t="s">
+        <v>25</v>
+      </c>
+      <c r="F42" t="s">
+        <v>25</v>
+      </c>
+      <c r="G42" t="s">
+        <v>25</v>
+      </c>
+      <c r="H42" t="s">
+        <v>25</v>
+      </c>
+      <c r="I42" t="s">
+        <v>25</v>
+      </c>
+      <c r="J42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K42" t="s">
+        <v>121</v>
+      </c>
+      <c r="L42" t="s">
+        <v>122</v>
+      </c>
+      <c r="M42" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>25</v>
+      </c>
+      <c r="B43" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" t="s">
+        <v>25</v>
+      </c>
+      <c r="D43" t="s">
+        <v>25</v>
+      </c>
+      <c r="E43" t="s">
+        <v>25</v>
+      </c>
+      <c r="F43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G43" t="s">
+        <v>25</v>
+      </c>
+      <c r="H43" t="s">
+        <v>25</v>
+      </c>
+      <c r="I43" t="s">
+        <v>25</v>
+      </c>
+      <c r="J43" t="s">
+        <v>25</v>
+      </c>
+      <c r="K43" t="s">
+        <v>123</v>
+      </c>
+      <c r="L43" t="s">
+        <v>124</v>
+      </c>
+      <c r="M43" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>25</v>
+      </c>
+      <c r="B44" t="s">
+        <v>25</v>
+      </c>
+      <c r="C44" t="s">
+        <v>25</v>
+      </c>
+      <c r="D44" t="s">
+        <v>25</v>
+      </c>
+      <c r="E44" t="s">
+        <v>25</v>
+      </c>
+      <c r="F44" t="s">
+        <v>25</v>
+      </c>
+      <c r="G44" t="s">
+        <v>25</v>
+      </c>
+      <c r="H44" t="s">
+        <v>25</v>
+      </c>
+      <c r="I44" t="s">
+        <v>25</v>
+      </c>
+      <c r="J44" t="s">
+        <v>25</v>
+      </c>
+      <c r="K44" t="s">
+        <v>125</v>
+      </c>
+      <c r="L44" t="s">
+        <v>126</v>
+      </c>
+      <c r="M44" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>25</v>
+      </c>
+      <c r="B45" t="s">
+        <v>25</v>
+      </c>
+      <c r="C45" t="s">
+        <v>25</v>
+      </c>
+      <c r="D45" t="s">
+        <v>25</v>
+      </c>
+      <c r="E45" t="s">
+        <v>25</v>
+      </c>
+      <c r="F45" t="s">
+        <v>25</v>
+      </c>
+      <c r="G45" t="s">
+        <v>25</v>
+      </c>
+      <c r="H45" t="s">
+        <v>25</v>
+      </c>
+      <c r="I45" t="s">
+        <v>25</v>
+      </c>
+      <c r="J45" t="s">
+        <v>25</v>
+      </c>
+      <c r="K45" t="s">
+        <v>70</v>
+      </c>
+      <c r="L45" t="s">
+        <v>71</v>
+      </c>
+      <c r="M45" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>127</v>
+      </c>
+      <c r="B46" t="s">
+        <v>128</v>
+      </c>
+      <c r="C46" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" t="s">
+        <v>17</v>
+      </c>
+      <c r="F46" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" t="s">
+        <v>19</v>
+      </c>
+      <c r="H46" t="s">
+        <v>20</v>
+      </c>
+      <c r="I46" t="s">
+        <v>21</v>
+      </c>
+      <c r="J46" t="s">
+        <v>129</v>
+      </c>
+      <c r="K46" t="s">
+        <v>130</v>
+      </c>
+      <c r="L46" t="s">
+        <v>92</v>
+      </c>
+      <c r="M46" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>25</v>
+      </c>
+      <c r="B47" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" t="s">
+        <v>25</v>
+      </c>
+      <c r="D47" t="s">
+        <v>25</v>
+      </c>
+      <c r="E47" t="s">
+        <v>25</v>
+      </c>
+      <c r="F47" t="s">
+        <v>25</v>
+      </c>
+      <c r="G47" t="s">
+        <v>25</v>
+      </c>
+      <c r="H47" t="s">
+        <v>25</v>
+      </c>
+      <c r="I47" t="s">
+        <v>25</v>
+      </c>
+      <c r="J47" t="s">
+        <v>25</v>
+      </c>
+      <c r="K47" t="s">
+        <v>131</v>
+      </c>
+      <c r="L47" t="s">
+        <v>132</v>
+      </c>
+      <c r="M47" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>25</v>
+      </c>
+      <c r="B48" t="s">
+        <v>25</v>
+      </c>
+      <c r="C48" t="s">
+        <v>25</v>
+      </c>
+      <c r="D48" t="s">
+        <v>25</v>
+      </c>
+      <c r="E48" t="s">
+        <v>25</v>
+      </c>
+      <c r="F48" t="s">
+        <v>25</v>
+      </c>
+      <c r="G48" t="s">
+        <v>25</v>
+      </c>
+      <c r="H48" t="s">
+        <v>25</v>
+      </c>
+      <c r="I48" t="s">
+        <v>25</v>
+      </c>
+      <c r="J48" t="s">
+        <v>25</v>
+      </c>
+      <c r="K48" t="s">
+        <v>133</v>
+      </c>
+      <c r="L48" t="s">
+        <v>134</v>
+      </c>
+      <c r="M48" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>25</v>
+      </c>
+      <c r="B49" t="s">
+        <v>25</v>
+      </c>
+      <c r="C49" t="s">
+        <v>25</v>
+      </c>
+      <c r="D49" t="s">
+        <v>25</v>
+      </c>
+      <c r="E49" t="s">
+        <v>25</v>
+      </c>
+      <c r="F49" t="s">
+        <v>25</v>
+      </c>
+      <c r="G49" t="s">
+        <v>25</v>
+      </c>
+      <c r="H49" t="s">
+        <v>25</v>
+      </c>
+      <c r="I49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J49" t="s">
+        <v>25</v>
+      </c>
+      <c r="K49" t="s">
+        <v>79</v>
+      </c>
+      <c r="L49" t="s">
+        <v>135</v>
+      </c>
+      <c r="M49" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>136</v>
+      </c>
+      <c r="B50" t="s">
+        <v>137</v>
+      </c>
+      <c r="C50" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" t="s">
+        <v>16</v>
+      </c>
+      <c r="E50" t="s">
+        <v>17</v>
+      </c>
+      <c r="F50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" t="s">
+        <v>19</v>
+      </c>
+      <c r="H50" t="s">
+        <v>20</v>
+      </c>
+      <c r="I50" t="s">
+        <v>21</v>
+      </c>
+      <c r="J50" t="s">
+        <v>129</v>
+      </c>
+      <c r="K50" t="s">
+        <v>138</v>
+      </c>
+      <c r="L50" t="s">
+        <v>92</v>
+      </c>
+      <c r="M50" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>25</v>
+      </c>
+      <c r="B51" t="s">
+        <v>25</v>
+      </c>
+      <c r="C51" t="s">
+        <v>25</v>
+      </c>
+      <c r="D51" t="s">
+        <v>25</v>
+      </c>
+      <c r="E51" t="s">
+        <v>25</v>
+      </c>
+      <c r="F51" t="s">
+        <v>25</v>
+      </c>
+      <c r="G51" t="s">
+        <v>25</v>
+      </c>
+      <c r="H51" t="s">
+        <v>25</v>
+      </c>
+      <c r="I51" t="s">
+        <v>25</v>
+      </c>
+      <c r="J51" t="s">
+        <v>25</v>
+      </c>
+      <c r="K51" t="s">
+        <v>131</v>
+      </c>
+      <c r="L51" t="s">
+        <v>139</v>
+      </c>
+      <c r="M51" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>25</v>
+      </c>
+      <c r="B52" t="s">
+        <v>25</v>
+      </c>
+      <c r="C52" t="s">
+        <v>25</v>
+      </c>
+      <c r="D52" t="s">
+        <v>25</v>
+      </c>
+      <c r="E52" t="s">
+        <v>25</v>
+      </c>
+      <c r="F52" t="s">
+        <v>25</v>
+      </c>
+      <c r="G52" t="s">
+        <v>25</v>
+      </c>
+      <c r="H52" t="s">
+        <v>25</v>
+      </c>
+      <c r="I52" t="s">
+        <v>25</v>
+      </c>
+      <c r="J52" t="s">
+        <v>25</v>
+      </c>
+      <c r="K52" t="s">
+        <v>101</v>
+      </c>
+      <c r="L52" t="s">
+        <v>135</v>
+      </c>
+      <c r="M52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>140</v>
+      </c>
+      <c r="B53" t="s">
+        <v>141</v>
+      </c>
+      <c r="C53" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" t="s">
+        <v>16</v>
+      </c>
+      <c r="E53" t="s">
+        <v>142</v>
+      </c>
+      <c r="F53" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" t="s">
+        <v>19</v>
+      </c>
+      <c r="H53" t="s">
+        <v>20</v>
+      </c>
+      <c r="I53" t="s">
+        <v>21</v>
+      </c>
+      <c r="J53" t="s">
+        <v>34</v>
+      </c>
+      <c r="K53" t="s">
+        <v>143</v>
+      </c>
+      <c r="L53" t="s">
+        <v>144</v>
+      </c>
+      <c r="M53" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>25</v>
+      </c>
+      <c r="B54" t="s">
+        <v>25</v>
+      </c>
+      <c r="C54" t="s">
+        <v>25</v>
+      </c>
+      <c r="D54" t="s">
+        <v>25</v>
+      </c>
+      <c r="E54" t="s">
+        <v>25</v>
+      </c>
+      <c r="F54" t="s">
+        <v>25</v>
+      </c>
+      <c r="G54" t="s">
+        <v>25</v>
+      </c>
+      <c r="H54" t="s">
+        <v>25</v>
+      </c>
+      <c r="I54" t="s">
+        <v>25</v>
+      </c>
+      <c r="J54" t="s">
+        <v>25</v>
+      </c>
+      <c r="K54" t="s">
+        <v>145</v>
+      </c>
+      <c r="L54" t="s">
+        <v>146</v>
+      </c>
+      <c r="M54" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>25</v>
+      </c>
+      <c r="B55" t="s">
+        <v>25</v>
+      </c>
+      <c r="C55" t="s">
+        <v>25</v>
+      </c>
+      <c r="D55" t="s">
+        <v>25</v>
+      </c>
+      <c r="E55" t="s">
+        <v>25</v>
+      </c>
+      <c r="F55" t="s">
+        <v>25</v>
+      </c>
+      <c r="G55" t="s">
+        <v>25</v>
+      </c>
+      <c r="H55" t="s">
+        <v>25</v>
+      </c>
+      <c r="I55" t="s">
+        <v>25</v>
+      </c>
+      <c r="J55" t="s">
+        <v>25</v>
+      </c>
+      <c r="K55" t="s">
+        <v>147</v>
+      </c>
+      <c r="L55" t="s">
+        <v>148</v>
+      </c>
+      <c r="M55" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>25</v>
+      </c>
+      <c r="B56" t="s">
+        <v>25</v>
+      </c>
+      <c r="C56" t="s">
+        <v>25</v>
+      </c>
+      <c r="D56" t="s">
+        <v>25</v>
+      </c>
+      <c r="E56" t="s">
+        <v>25</v>
+      </c>
+      <c r="F56" t="s">
+        <v>25</v>
+      </c>
+      <c r="G56" t="s">
+        <v>25</v>
+      </c>
+      <c r="H56" t="s">
+        <v>25</v>
+      </c>
+      <c r="I56" t="s">
+        <v>25</v>
+      </c>
+      <c r="J56" t="s">
+        <v>25</v>
+      </c>
+      <c r="K56" t="s">
+        <v>149</v>
+      </c>
+      <c r="L56" t="s">
+        <v>150</v>
+      </c>
+      <c r="M56" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>25</v>
+      </c>
+      <c r="B57" t="s">
+        <v>25</v>
+      </c>
+      <c r="C57" t="s">
+        <v>25</v>
+      </c>
+      <c r="D57" t="s">
+        <v>25</v>
+      </c>
+      <c r="E57" t="s">
+        <v>25</v>
+      </c>
+      <c r="F57" t="s">
+        <v>25</v>
+      </c>
+      <c r="G57" t="s">
+        <v>25</v>
+      </c>
+      <c r="H57" t="s">
+        <v>25</v>
+      </c>
+      <c r="I57" t="s">
+        <v>25</v>
+      </c>
+      <c r="J57" t="s">
+        <v>25</v>
+      </c>
+      <c r="K57" t="s">
+        <v>151</v>
+      </c>
+      <c r="L57" t="s">
+        <v>152</v>
+      </c>
+      <c r="M57" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>25</v>
+      </c>
+      <c r="B58" t="s">
+        <v>25</v>
+      </c>
+      <c r="C58" t="s">
+        <v>25</v>
+      </c>
+      <c r="D58" t="s">
+        <v>25</v>
+      </c>
+      <c r="E58" t="s">
+        <v>25</v>
+      </c>
+      <c r="F58" t="s">
+        <v>25</v>
+      </c>
+      <c r="G58" t="s">
+        <v>25</v>
+      </c>
+      <c r="H58" t="s">
+        <v>25</v>
+      </c>
+      <c r="I58" t="s">
+        <v>25</v>
+      </c>
+      <c r="J58" t="s">
+        <v>25</v>
+      </c>
+      <c r="K58" t="s">
+        <v>93</v>
+      </c>
+      <c r="L58" t="s">
+        <v>153</v>
+      </c>
+      <c r="M58" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>154</v>
+      </c>
+      <c r="B59" t="s">
+        <v>155</v>
+      </c>
+      <c r="C59" t="s">
+        <v>15</v>
+      </c>
+      <c r="D59" t="s">
+        <v>16</v>
+      </c>
+      <c r="E59" t="s">
+        <v>17</v>
+      </c>
+      <c r="F59" t="s">
+        <v>18</v>
+      </c>
+      <c r="G59" t="s">
+        <v>19</v>
+      </c>
+      <c r="H59" t="s">
+        <v>20</v>
+      </c>
+      <c r="I59" t="s">
+        <v>21</v>
+      </c>
+      <c r="J59" t="s">
+        <v>34</v>
+      </c>
+      <c r="K59" t="s">
+        <v>156</v>
+      </c>
+      <c r="L59" t="s">
+        <v>157</v>
+      </c>
+      <c r="M59" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>25</v>
+      </c>
+      <c r="B60" t="s">
+        <v>25</v>
+      </c>
+      <c r="C60" t="s">
+        <v>25</v>
+      </c>
+      <c r="D60" t="s">
+        <v>25</v>
+      </c>
+      <c r="E60" t="s">
+        <v>25</v>
+      </c>
+      <c r="F60" t="s">
+        <v>25</v>
+      </c>
+      <c r="G60" t="s">
+        <v>25</v>
+      </c>
+      <c r="H60" t="s">
+        <v>25</v>
+      </c>
+      <c r="I60" t="s">
+        <v>25</v>
+      </c>
+      <c r="J60" t="s">
+        <v>25</v>
+      </c>
+      <c r="K60" t="s">
+        <v>158</v>
+      </c>
+      <c r="L60" t="s">
+        <v>159</v>
+      </c>
+      <c r="M60" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>25</v>
+      </c>
+      <c r="B61" t="s">
+        <v>25</v>
+      </c>
+      <c r="C61" t="s">
+        <v>25</v>
+      </c>
+      <c r="D61" t="s">
+        <v>25</v>
+      </c>
+      <c r="E61" t="s">
+        <v>25</v>
+      </c>
+      <c r="F61" t="s">
+        <v>25</v>
+      </c>
+      <c r="G61" t="s">
+        <v>25</v>
+      </c>
+      <c r="H61" t="s">
+        <v>25</v>
+      </c>
+      <c r="I61" t="s">
+        <v>25</v>
+      </c>
+      <c r="J61" t="s">
+        <v>25</v>
+      </c>
+      <c r="K61" t="s">
+        <v>160</v>
+      </c>
+      <c r="L61" t="s">
+        <v>161</v>
+      </c>
+      <c r="M61" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>25</v>
+      </c>
+      <c r="B62" t="s">
+        <v>25</v>
+      </c>
+      <c r="C62" t="s">
+        <v>25</v>
+      </c>
+      <c r="D62" t="s">
+        <v>25</v>
+      </c>
+      <c r="E62" t="s">
+        <v>25</v>
+      </c>
+      <c r="F62" t="s">
+        <v>25</v>
+      </c>
+      <c r="G62" t="s">
+        <v>25</v>
+      </c>
+      <c r="H62" t="s">
+        <v>25</v>
+      </c>
+      <c r="I62" t="s">
+        <v>25</v>
+      </c>
+      <c r="J62" t="s">
+        <v>25</v>
+      </c>
+      <c r="K62" t="s">
+        <v>79</v>
+      </c>
+      <c r="L62" t="s">
+        <v>153</v>
+      </c>
+      <c r="M62" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>162</v>
+      </c>
+      <c r="B63" t="s">
+        <v>163</v>
+      </c>
+      <c r="C63" t="s">
+        <v>15</v>
+      </c>
+      <c r="D63" t="s">
+        <v>16</v>
+      </c>
+      <c r="E63" t="s">
+        <v>17</v>
+      </c>
+      <c r="F63" t="s">
+        <v>18</v>
+      </c>
+      <c r="G63" t="s">
+        <v>19</v>
+      </c>
+      <c r="H63" t="s">
+        <v>20</v>
+      </c>
+      <c r="I63" t="s">
+        <v>21</v>
+      </c>
+      <c r="J63" t="s">
+        <v>34</v>
+      </c>
+      <c r="K63" t="s">
+        <v>164</v>
+      </c>
+      <c r="L63" t="s">
+        <v>165</v>
+      </c>
+      <c r="M63" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>25</v>
+      </c>
+      <c r="B64" t="s">
+        <v>25</v>
+      </c>
+      <c r="C64" t="s">
+        <v>25</v>
+      </c>
+      <c r="D64" t="s">
+        <v>25</v>
+      </c>
+      <c r="E64" t="s">
+        <v>25</v>
+      </c>
+      <c r="F64" t="s">
+        <v>25</v>
+      </c>
+      <c r="G64" t="s">
+        <v>25</v>
+      </c>
+      <c r="H64" t="s">
+        <v>25</v>
+      </c>
+      <c r="I64" t="s">
+        <v>25</v>
+      </c>
+      <c r="J64" t="s">
+        <v>25</v>
+      </c>
+      <c r="K64" t="s">
+        <v>166</v>
+      </c>
+      <c r="L64" t="s">
+        <v>167</v>
+      </c>
+      <c r="M64" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>25</v>
+      </c>
+      <c r="B65" t="s">
+        <v>25</v>
+      </c>
+      <c r="C65" t="s">
+        <v>25</v>
+      </c>
+      <c r="D65" t="s">
+        <v>25</v>
+      </c>
+      <c r="E65" t="s">
+        <v>25</v>
+      </c>
+      <c r="F65" t="s">
+        <v>25</v>
+      </c>
+      <c r="G65" t="s">
+        <v>25</v>
+      </c>
+      <c r="H65" t="s">
+        <v>25</v>
+      </c>
+      <c r="I65" t="s">
+        <v>25</v>
+      </c>
+      <c r="J65" t="s">
+        <v>25</v>
+      </c>
+      <c r="K65" t="s">
+        <v>168</v>
+      </c>
+      <c r="L65" t="s">
+        <v>169</v>
+      </c>
+      <c r="M65" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>25</v>
+      </c>
+      <c r="B66" t="s">
+        <v>25</v>
+      </c>
+      <c r="C66" t="s">
+        <v>25</v>
+      </c>
+      <c r="D66" t="s">
+        <v>25</v>
+      </c>
+      <c r="E66" t="s">
+        <v>25</v>
+      </c>
+      <c r="F66" t="s">
+        <v>25</v>
+      </c>
+      <c r="G66" t="s">
+        <v>25</v>
+      </c>
+      <c r="H66" t="s">
+        <v>25</v>
+      </c>
+      <c r="I66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J66" t="s">
+        <v>25</v>
+      </c>
+      <c r="K66" t="s">
+        <v>79</v>
+      </c>
+      <c r="L66" t="s">
+        <v>153</v>
+      </c>
+      <c r="M66" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>170</v>
+      </c>
+      <c r="B67" t="s">
+        <v>171</v>
+      </c>
+      <c r="C67" t="s">
+        <v>15</v>
+      </c>
+      <c r="D67" t="s">
+        <v>16</v>
+      </c>
+      <c r="E67" t="s">
+        <v>172</v>
+      </c>
+      <c r="F67" t="s">
+        <v>18</v>
+      </c>
+      <c r="G67" t="s">
+        <v>19</v>
+      </c>
+      <c r="H67" t="s">
+        <v>20</v>
+      </c>
+      <c r="I67" t="s">
+        <v>21</v>
+      </c>
+      <c r="J67" t="s">
+        <v>34</v>
+      </c>
+      <c r="K67" t="s">
+        <v>173</v>
+      </c>
+      <c r="L67" t="s">
+        <v>174</v>
+      </c>
+      <c r="M67" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>25</v>
+      </c>
+      <c r="B68" t="s">
+        <v>25</v>
+      </c>
+      <c r="C68" t="s">
+        <v>25</v>
+      </c>
+      <c r="D68" t="s">
+        <v>25</v>
+      </c>
+      <c r="E68" t="s">
+        <v>25</v>
+      </c>
+      <c r="F68" t="s">
+        <v>25</v>
+      </c>
+      <c r="G68" t="s">
+        <v>25</v>
+      </c>
+      <c r="H68" t="s">
+        <v>25</v>
+      </c>
+      <c r="I68" t="s">
+        <v>25</v>
+      </c>
+      <c r="J68" t="s">
+        <v>25</v>
+      </c>
+      <c r="K68" t="s">
+        <v>175</v>
+      </c>
+      <c r="L68" t="s">
+        <v>176</v>
+      </c>
+      <c r="M68" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>25</v>
+      </c>
+      <c r="B69" t="s">
+        <v>25</v>
+      </c>
+      <c r="C69" t="s">
+        <v>25</v>
+      </c>
+      <c r="D69" t="s">
+        <v>25</v>
+      </c>
+      <c r="E69" t="s">
+        <v>25</v>
+      </c>
+      <c r="F69" t="s">
+        <v>25</v>
+      </c>
+      <c r="G69" t="s">
+        <v>25</v>
+      </c>
+      <c r="H69" t="s">
+        <v>25</v>
+      </c>
+      <c r="I69" t="s">
+        <v>25</v>
+      </c>
+      <c r="J69" t="s">
+        <v>25</v>
+      </c>
+      <c r="K69" t="s">
+        <v>177</v>
+      </c>
+      <c r="L69" t="s">
+        <v>178</v>
+      </c>
+      <c r="M69" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>25</v>
+      </c>
+      <c r="B70" t="s">
+        <v>25</v>
+      </c>
+      <c r="C70" t="s">
+        <v>25</v>
+      </c>
+      <c r="D70" t="s">
+        <v>25</v>
+      </c>
+      <c r="E70" t="s">
+        <v>25</v>
+      </c>
+      <c r="F70" t="s">
+        <v>25</v>
+      </c>
+      <c r="G70" t="s">
+        <v>25</v>
+      </c>
+      <c r="H70" t="s">
+        <v>25</v>
+      </c>
+      <c r="I70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J70" t="s">
+        <v>25</v>
+      </c>
+      <c r="K70" t="s">
+        <v>79</v>
+      </c>
+      <c r="L70" t="s">
+        <v>153</v>
+      </c>
+      <c r="M70" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>179</v>
+      </c>
+      <c r="B71" t="s">
+        <v>180</v>
+      </c>
+      <c r="C71" t="s">
+        <v>15</v>
+      </c>
+      <c r="D71" t="s">
+        <v>16</v>
+      </c>
+      <c r="E71" t="s">
+        <v>17</v>
+      </c>
+      <c r="F71" t="s">
+        <v>18</v>
+      </c>
+      <c r="G71" t="s">
+        <v>19</v>
+      </c>
+      <c r="H71" t="s">
+        <v>20</v>
+      </c>
+      <c r="I71" t="s">
+        <v>21</v>
+      </c>
+      <c r="J71" t="s">
+        <v>34</v>
+      </c>
+      <c r="K71" t="s">
+        <v>181</v>
+      </c>
+      <c r="L71" t="s">
+        <v>182</v>
+      </c>
+      <c r="M71" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>25</v>
+      </c>
+      <c r="B72" t="s">
+        <v>25</v>
+      </c>
+      <c r="C72" t="s">
+        <v>25</v>
+      </c>
+      <c r="D72" t="s">
+        <v>25</v>
+      </c>
+      <c r="E72" t="s">
+        <v>25</v>
+      </c>
+      <c r="F72" t="s">
+        <v>25</v>
+      </c>
+      <c r="G72" t="s">
+        <v>25</v>
+      </c>
+      <c r="H72" t="s">
+        <v>25</v>
+      </c>
+      <c r="I72" t="s">
+        <v>25</v>
+      </c>
+      <c r="J72" t="s">
+        <v>25</v>
+      </c>
+      <c r="K72" t="s">
+        <v>183</v>
+      </c>
+      <c r="L72" t="s">
+        <v>184</v>
+      </c>
+      <c r="M72" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>25</v>
+      </c>
+      <c r="B73" t="s">
+        <v>25</v>
+      </c>
+      <c r="C73" t="s">
+        <v>25</v>
+      </c>
+      <c r="D73" t="s">
+        <v>25</v>
+      </c>
+      <c r="E73" t="s">
+        <v>25</v>
+      </c>
+      <c r="F73" t="s">
+        <v>25</v>
+      </c>
+      <c r="G73" t="s">
+        <v>25</v>
+      </c>
+      <c r="H73" t="s">
+        <v>25</v>
+      </c>
+      <c r="I73" t="s">
+        <v>25</v>
+      </c>
+      <c r="J73" t="s">
+        <v>25</v>
+      </c>
+      <c r="K73" t="s">
+        <v>185</v>
+      </c>
+      <c r="L73" t="s">
+        <v>186</v>
+      </c>
+      <c r="M73" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>25</v>
+      </c>
+      <c r="B74" t="s">
+        <v>25</v>
+      </c>
+      <c r="C74" t="s">
+        <v>25</v>
+      </c>
+      <c r="D74" t="s">
+        <v>25</v>
+      </c>
+      <c r="E74" t="s">
+        <v>25</v>
+      </c>
+      <c r="F74" t="s">
+        <v>25</v>
+      </c>
+      <c r="G74" t="s">
+        <v>25</v>
+      </c>
+      <c r="H74" t="s">
+        <v>25</v>
+      </c>
+      <c r="I74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J74" t="s">
+        <v>25</v>
+      </c>
+      <c r="K74" t="s">
+        <v>79</v>
+      </c>
+      <c r="L74" t="s">
+        <v>153</v>
+      </c>
+      <c r="M74" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>187</v>
+      </c>
+      <c r="B75" t="s">
+        <v>188</v>
+      </c>
+      <c r="C75" t="s">
+        <v>15</v>
+      </c>
+      <c r="D75" t="s">
+        <v>16</v>
+      </c>
+      <c r="E75" t="s">
+        <v>17</v>
+      </c>
+      <c r="F75" t="s">
+        <v>18</v>
+      </c>
+      <c r="G75" t="s">
+        <v>19</v>
+      </c>
+      <c r="H75" t="s">
+        <v>20</v>
+      </c>
+      <c r="I75" t="s">
+        <v>21</v>
+      </c>
+      <c r="J75" t="s">
+        <v>189</v>
+      </c>
+      <c r="K75" t="s">
+        <v>190</v>
+      </c>
+      <c r="L75" t="s">
+        <v>191</v>
+      </c>
+      <c r="M75" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>25</v>
+      </c>
+      <c r="B76" t="s">
+        <v>25</v>
+      </c>
+      <c r="C76" t="s">
+        <v>25</v>
+      </c>
+      <c r="D76" t="s">
+        <v>25</v>
+      </c>
+      <c r="E76" t="s">
+        <v>25</v>
+      </c>
+      <c r="F76" t="s">
+        <v>25</v>
+      </c>
+      <c r="G76" t="s">
+        <v>25</v>
+      </c>
+      <c r="H76" t="s">
+        <v>25</v>
+      </c>
+      <c r="I76" t="s">
+        <v>25</v>
+      </c>
+      <c r="J76" t="s">
+        <v>25</v>
+      </c>
+      <c r="K76" t="s">
+        <v>192</v>
+      </c>
+      <c r="L76" t="s">
+        <v>153</v>
+      </c>
+      <c r="M76" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>193</v>
+      </c>
+      <c r="B77" t="s">
+        <v>194</v>
+      </c>
+      <c r="C77" t="s">
+        <v>15</v>
+      </c>
+      <c r="D77" t="s">
+        <v>16</v>
+      </c>
+      <c r="E77" t="s">
+        <v>195</v>
+      </c>
+      <c r="F77" t="s">
+        <v>18</v>
+      </c>
+      <c r="G77" t="s">
+        <v>19</v>
+      </c>
+      <c r="H77" t="s">
+        <v>20</v>
+      </c>
+      <c r="I77" t="s">
+        <v>21</v>
+      </c>
+      <c r="J77" t="s">
+        <v>34</v>
+      </c>
+      <c r="K77" t="s">
+        <v>196</v>
+      </c>
+      <c r="L77" t="s">
+        <v>197</v>
+      </c>
+      <c r="M77" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>25</v>
+      </c>
+      <c r="B78" t="s">
+        <v>25</v>
+      </c>
+      <c r="C78" t="s">
+        <v>25</v>
+      </c>
+      <c r="D78" t="s">
+        <v>25</v>
+      </c>
+      <c r="E78" t="s">
+        <v>25</v>
+      </c>
+      <c r="F78" t="s">
+        <v>25</v>
+      </c>
+      <c r="G78" t="s">
+        <v>25</v>
+      </c>
+      <c r="H78" t="s">
+        <v>25</v>
+      </c>
+      <c r="I78" t="s">
+        <v>25</v>
+      </c>
+      <c r="J78" t="s">
+        <v>25</v>
+      </c>
+      <c r="K78" t="s">
+        <v>198</v>
+      </c>
+      <c r="L78" t="s">
+        <v>199</v>
+      </c>
+      <c r="M78" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>25</v>
+      </c>
+      <c r="B79" t="s">
+        <v>25</v>
+      </c>
+      <c r="C79" t="s">
+        <v>25</v>
+      </c>
+      <c r="D79" t="s">
+        <v>25</v>
+      </c>
+      <c r="E79" t="s">
+        <v>25</v>
+      </c>
+      <c r="F79" t="s">
+        <v>25</v>
+      </c>
+      <c r="G79" t="s">
+        <v>25</v>
+      </c>
+      <c r="H79" t="s">
+        <v>25</v>
+      </c>
+      <c r="I79" t="s">
+        <v>25</v>
+      </c>
+      <c r="J79" t="s">
+        <v>25</v>
+      </c>
+      <c r="K79" t="s">
+        <v>200</v>
+      </c>
+      <c r="L79" t="s">
+        <v>201</v>
+      </c>
+      <c r="M79" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>25</v>
+      </c>
+      <c r="B80" t="s">
+        <v>25</v>
+      </c>
+      <c r="C80" t="s">
+        <v>25</v>
+      </c>
+      <c r="D80" t="s">
+        <v>25</v>
+      </c>
+      <c r="E80" t="s">
+        <v>25</v>
+      </c>
+      <c r="F80" t="s">
+        <v>25</v>
+      </c>
+      <c r="G80" t="s">
+        <v>25</v>
+      </c>
+      <c r="H80" t="s">
+        <v>25</v>
+      </c>
+      <c r="I80" t="s">
+        <v>25</v>
+      </c>
+      <c r="J80" t="s">
+        <v>25</v>
+      </c>
+      <c r="K80" t="s">
+        <v>79</v>
+      </c>
+      <c r="L80" t="s">
+        <v>153</v>
+      </c>
+      <c r="M80" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>202</v>
+      </c>
+      <c r="B81" t="s">
+        <v>203</v>
+      </c>
+      <c r="C81" t="s">
+        <v>15</v>
+      </c>
+      <c r="D81" t="s">
+        <v>16</v>
+      </c>
+      <c r="E81" t="s">
+        <v>17</v>
+      </c>
+      <c r="F81" t="s">
+        <v>18</v>
+      </c>
+      <c r="G81" t="s">
+        <v>19</v>
+      </c>
+      <c r="H81" t="s">
+        <v>20</v>
+      </c>
+      <c r="I81" t="s">
+        <v>21</v>
+      </c>
+      <c r="J81" t="s">
+        <v>48</v>
+      </c>
+      <c r="K81" t="s">
+        <v>23</v>
+      </c>
+      <c r="L81" t="s">
+        <v>204</v>
+      </c>
+      <c r="M81" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>25</v>
+      </c>
+      <c r="B82" t="s">
+        <v>25</v>
+      </c>
+      <c r="C82" t="s">
+        <v>25</v>
+      </c>
+      <c r="D82" t="s">
+        <v>25</v>
+      </c>
+      <c r="E82" t="s">
+        <v>25</v>
+      </c>
+      <c r="F82" t="s">
+        <v>25</v>
+      </c>
+      <c r="G82" t="s">
+        <v>25</v>
+      </c>
+      <c r="H82" t="s">
+        <v>25</v>
+      </c>
+      <c r="I82" t="s">
+        <v>25</v>
+      </c>
+      <c r="J82" t="s">
+        <v>25</v>
+      </c>
+      <c r="K82" t="s">
+        <v>205</v>
+      </c>
+      <c r="L82" t="s">
+        <v>206</v>
+      </c>
+      <c r="M82" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>25</v>
+      </c>
+      <c r="B83" t="s">
+        <v>25</v>
+      </c>
+      <c r="C83" t="s">
+        <v>25</v>
+      </c>
+      <c r="D83" t="s">
+        <v>25</v>
+      </c>
+      <c r="E83" t="s">
+        <v>25</v>
+      </c>
+      <c r="F83" t="s">
+        <v>25</v>
+      </c>
+      <c r="G83" t="s">
+        <v>25</v>
+      </c>
+      <c r="H83" t="s">
+        <v>25</v>
+      </c>
+      <c r="I83" t="s">
+        <v>25</v>
+      </c>
+      <c r="J83" t="s">
+        <v>25</v>
+      </c>
+      <c r="K83" t="s">
+        <v>207</v>
+      </c>
+      <c r="L83" t="s">
+        <v>150</v>
+      </c>
+      <c r="M83" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>25</v>
+      </c>
+      <c r="B84" t="s">
+        <v>25</v>
+      </c>
+      <c r="C84" t="s">
+        <v>25</v>
+      </c>
+      <c r="D84" t="s">
+        <v>25</v>
+      </c>
+      <c r="E84" t="s">
+        <v>25</v>
+      </c>
+      <c r="F84" t="s">
+        <v>25</v>
+      </c>
+      <c r="G84" t="s">
+        <v>25</v>
+      </c>
+      <c r="H84" t="s">
+        <v>25</v>
+      </c>
+      <c r="I84" t="s">
+        <v>25</v>
+      </c>
+      <c r="J84" t="s">
+        <v>25</v>
+      </c>
+      <c r="K84" t="s">
+        <v>208</v>
+      </c>
+      <c r="L84" t="s">
+        <v>209</v>
+      </c>
+      <c r="M84" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>25</v>
+      </c>
+      <c r="B85" t="s">
+        <v>25</v>
+      </c>
+      <c r="C85" t="s">
+        <v>25</v>
+      </c>
+      <c r="D85" t="s">
+        <v>25</v>
+      </c>
+      <c r="E85" t="s">
+        <v>25</v>
+      </c>
+      <c r="F85" t="s">
+        <v>25</v>
+      </c>
+      <c r="G85" t="s">
+        <v>25</v>
+      </c>
+      <c r="H85" t="s">
+        <v>25</v>
+      </c>
+      <c r="I85" t="s">
+        <v>25</v>
+      </c>
+      <c r="J85" t="s">
+        <v>25</v>
+      </c>
+      <c r="K85" t="s">
+        <v>210</v>
+      </c>
+      <c r="L85" t="s">
+        <v>25</v>
+      </c>
+      <c r="M85" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>211</v>
+      </c>
+      <c r="B86" t="s">
+        <v>212</v>
+      </c>
+      <c r="C86" t="s">
+        <v>15</v>
+      </c>
+      <c r="D86" t="s">
+        <v>16</v>
+      </c>
+      <c r="E86" t="s">
+        <v>213</v>
+      </c>
+      <c r="F86" t="s">
+        <v>18</v>
+      </c>
+      <c r="G86" t="s">
+        <v>19</v>
+      </c>
+      <c r="H86" t="s">
+        <v>20</v>
+      </c>
+      <c r="I86" t="s">
+        <v>21</v>
+      </c>
+      <c r="J86" t="s">
+        <v>48</v>
+      </c>
+      <c r="K86" t="s">
+        <v>23</v>
+      </c>
+      <c r="L86" t="s">
+        <v>204</v>
+      </c>
+      <c r="M86" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>25</v>
+      </c>
+      <c r="B87" t="s">
+        <v>25</v>
+      </c>
+      <c r="C87" t="s">
+        <v>25</v>
+      </c>
+      <c r="D87" t="s">
+        <v>25</v>
+      </c>
+      <c r="E87" t="s">
+        <v>25</v>
+      </c>
+      <c r="F87" t="s">
+        <v>25</v>
+      </c>
+      <c r="G87" t="s">
+        <v>25</v>
+      </c>
+      <c r="H87" t="s">
+        <v>25</v>
+      </c>
+      <c r="I87" t="s">
+        <v>25</v>
+      </c>
+      <c r="J87" t="s">
+        <v>25</v>
+      </c>
+      <c r="K87" t="s">
+        <v>214</v>
+      </c>
+      <c r="L87" t="s">
+        <v>215</v>
+      </c>
+      <c r="M87" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>25</v>
+      </c>
+      <c r="B88" t="s">
+        <v>25</v>
+      </c>
+      <c r="C88" t="s">
+        <v>25</v>
+      </c>
+      <c r="D88" t="s">
+        <v>25</v>
+      </c>
+      <c r="E88" t="s">
+        <v>25</v>
+      </c>
+      <c r="F88" t="s">
+        <v>25</v>
+      </c>
+      <c r="G88" t="s">
+        <v>25</v>
+      </c>
+      <c r="H88" t="s">
+        <v>25</v>
+      </c>
+      <c r="I88" t="s">
+        <v>25</v>
+      </c>
+      <c r="J88" t="s">
+        <v>25</v>
+      </c>
+      <c r="K88" t="s">
+        <v>207</v>
+      </c>
+      <c r="L88" t="s">
+        <v>216</v>
+      </c>
+      <c r="M88" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>25</v>
+      </c>
+      <c r="B89" t="s">
+        <v>25</v>
+      </c>
+      <c r="C89" t="s">
+        <v>25</v>
+      </c>
+      <c r="D89" t="s">
+        <v>25</v>
+      </c>
+      <c r="E89" t="s">
+        <v>25</v>
+      </c>
+      <c r="F89" t="s">
+        <v>25</v>
+      </c>
+      <c r="G89" t="s">
+        <v>25</v>
+      </c>
+      <c r="H89" t="s">
+        <v>25</v>
+      </c>
+      <c r="I89" t="s">
+        <v>25</v>
+      </c>
+      <c r="J89" t="s">
+        <v>25</v>
+      </c>
+      <c r="K89" t="s">
+        <v>217</v>
+      </c>
+      <c r="L89" t="s">
+        <v>25</v>
+      </c>
+      <c r="M89" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>218</v>
+      </c>
+      <c r="B90" t="s">
+        <v>219</v>
+      </c>
+      <c r="C90" t="s">
+        <v>15</v>
+      </c>
+      <c r="D90" t="s">
+        <v>16</v>
+      </c>
+      <c r="E90" t="s">
+        <v>17</v>
+      </c>
+      <c r="F90" t="s">
+        <v>18</v>
+      </c>
+      <c r="G90" t="s">
+        <v>19</v>
+      </c>
+      <c r="H90" t="s">
+        <v>20</v>
+      </c>
+      <c r="I90" t="s">
+        <v>21</v>
+      </c>
+      <c r="J90" t="s">
+        <v>220</v>
+      </c>
+      <c r="K90" t="s">
+        <v>221</v>
+      </c>
+      <c r="L90" t="s">
+        <v>222</v>
+      </c>
+      <c r="M90" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>25</v>
+      </c>
+      <c r="B91" t="s">
+        <v>25</v>
+      </c>
+      <c r="C91" t="s">
+        <v>25</v>
+      </c>
+      <c r="D91" t="s">
+        <v>25</v>
+      </c>
+      <c r="E91" t="s">
+        <v>25</v>
+      </c>
+      <c r="F91" t="s">
+        <v>25</v>
+      </c>
+      <c r="G91" t="s">
+        <v>25</v>
+      </c>
+      <c r="H91" t="s">
+        <v>25</v>
+      </c>
+      <c r="I91" t="s">
+        <v>25</v>
+      </c>
+      <c r="J91" t="s">
+        <v>25</v>
+      </c>
+      <c r="K91" t="s">
+        <v>223</v>
+      </c>
+      <c r="L91" t="s">
+        <v>224</v>
+      </c>
+      <c r="M91" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>25</v>
+      </c>
+      <c r="B92" t="s">
+        <v>25</v>
+      </c>
+      <c r="C92" t="s">
+        <v>25</v>
+      </c>
+      <c r="D92" t="s">
+        <v>25</v>
+      </c>
+      <c r="E92" t="s">
+        <v>25</v>
+      </c>
+      <c r="F92" t="s">
+        <v>25</v>
+      </c>
+      <c r="G92" t="s">
+        <v>25</v>
+      </c>
+      <c r="H92" t="s">
+        <v>25</v>
+      </c>
+      <c r="I92" t="s">
+        <v>25</v>
+      </c>
+      <c r="J92" t="s">
+        <v>25</v>
+      </c>
+      <c r="K92" t="s">
+        <v>225</v>
+      </c>
+      <c r="L92" t="s">
+        <v>226</v>
+      </c>
+      <c r="M92" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>227</v>
+      </c>
+      <c r="B93" t="s">
+        <v>228</v>
+      </c>
+      <c r="C93" t="s">
+        <v>15</v>
+      </c>
+      <c r="D93" t="s">
+        <v>16</v>
+      </c>
+      <c r="E93" t="s">
+        <v>229</v>
+      </c>
+      <c r="F93" t="s">
+        <v>18</v>
+      </c>
+      <c r="G93" t="s">
+        <v>19</v>
+      </c>
+      <c r="H93" t="s">
+        <v>20</v>
+      </c>
+      <c r="I93" t="s">
+        <v>21</v>
+      </c>
+      <c r="J93" t="s">
+        <v>220</v>
+      </c>
+      <c r="K93" t="s">
+        <v>221</v>
+      </c>
+      <c r="L93" t="s">
+        <v>222</v>
+      </c>
+      <c r="M93" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>25</v>
+      </c>
+      <c r="B94" t="s">
+        <v>25</v>
+      </c>
+      <c r="C94" t="s">
+        <v>25</v>
+      </c>
+      <c r="D94" t="s">
+        <v>25</v>
+      </c>
+      <c r="E94" t="s">
+        <v>25</v>
+      </c>
+      <c r="F94" t="s">
+        <v>25</v>
+      </c>
+      <c r="G94" t="s">
+        <v>25</v>
+      </c>
+      <c r="H94" t="s">
+        <v>25</v>
+      </c>
+      <c r="I94" t="s">
+        <v>25</v>
+      </c>
+      <c r="J94" t="s">
+        <v>25</v>
+      </c>
+      <c r="K94" t="s">
+        <v>230</v>
+      </c>
+      <c r="L94" t="s">
+        <v>231</v>
+      </c>
+      <c r="M94" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>25</v>
+      </c>
+      <c r="B95" t="s">
+        <v>25</v>
+      </c>
+      <c r="C95" t="s">
+        <v>25</v>
+      </c>
+      <c r="D95" t="s">
+        <v>25</v>
+      </c>
+      <c r="E95" t="s">
+        <v>25</v>
+      </c>
+      <c r="F95" t="s">
+        <v>25</v>
+      </c>
+      <c r="G95" t="s">
+        <v>25</v>
+      </c>
+      <c r="H95" t="s">
+        <v>25</v>
+      </c>
+      <c r="I95" t="s">
+        <v>25</v>
+      </c>
+      <c r="J95" t="s">
+        <v>25</v>
+      </c>
+      <c r="K95" t="s">
+        <v>225</v>
+      </c>
+      <c r="L95" t="s">
+        <v>226</v>
+      </c>
+      <c r="M95" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="J97" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K97" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L97" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M97" s="2" t="s">
+        <v>236</v>
       </c>
     </row>
   </sheetData>

--- a/clients/encore/testcases/create-new-product-groups/item-search-create-new-product-groups.xlsx
+++ b/clients/encore/testcases/create-new-product-groups/item-search-create-new-product-groups.xlsx
@@ -52,7 +52,7 @@
     <t>Notes / Reason</t>
   </si>
   <si>
-    <t>TC-ISR-PGR-006</t>
+    <t>TC-ISR-APG-001</t>
   </si>
   <si>
     <t>The Add page opens with a held-back Save</t>
@@ -111,7 +111,7 @@
     <t>Save stays disabled — the other required fields are still empty</t>
   </si>
   <si>
-    <t>TC-ISR-PGR-007</t>
+    <t>TC-ISR-APG-002</t>
   </si>
   <si>
     <t>The sub-class picker shows its two panels</t>
@@ -132,7 +132,7 @@
     <t>It is marked required and shows the instruction "Drag or double‑click items from the left to add sub‑classes"</t>
   </si>
   <si>
-    <t>TC-ISR-PGR-008</t>
+    <t>TC-ISR-APG-003</t>
   </si>
   <si>
     <t>Cancel leaves the Add page without saving</t>
@@ -153,7 +153,7 @@
     <t>The form is empty again; nothing was kept</t>
   </si>
   <si>
-    <t>TC-ISR-PGR-011</t>
+    <t>TC-ISR-APG-004</t>
   </si>
   <si>
     <t>A completed Add page saves a new product group and it is found again</t>
@@ -192,7 +192,7 @@
     <t>Exactly one row returns — the group just created, showing its Description and Service Type</t>
   </si>
   <si>
-    <t>TC-ISR-PGR-012</t>
+    <t>TC-ISR-APG-005</t>
   </si>
   <si>
     <t>Name accepts exactly 50 characters and drops the rest silently</t>
@@ -231,7 +231,7 @@
     <t>The list page returns; nothing was saved</t>
   </si>
   <si>
-    <t>TC-ISR-PGR-013</t>
+    <t>TC-ISR-APG-006</t>
   </si>
   <si>
     <t>Description accepts exactly 100 characters and drops the rest silently</t>
@@ -255,7 +255,7 @@
     <t>4. Click Cancel</t>
   </si>
   <si>
-    <t>TC-ISR-PGR-014</t>
+    <t>TC-ISR-APG-007</t>
   </si>
   <si>
     <t>Clearing a filled Name by either method holds Save back and marks the box invalid</t>
@@ -297,7 +297,7 @@
     <t>6. Click Cancel</t>
   </si>
   <si>
-    <t>TC-ISR-PGR-015</t>
+    <t>TC-ISR-APG-008</t>
   </si>
   <si>
     <t>A whitespace-only Name counts as empty; a padded Name is accepted</t>
@@ -321,7 +321,7 @@
     <t>3. Click Cancel</t>
   </si>
   <si>
-    <t>TC-ISR-PGR-016</t>
+    <t>TC-ISR-APG-009</t>
   </si>
   <si>
     <t>Every required field gates Save, and Active does not</t>
@@ -363,7 +363,7 @@
     <t>8. Click Cancel</t>
   </si>
   <si>
-    <t>TC-ISR-PGR-017</t>
+    <t>TC-ISR-APG-010</t>
   </si>
   <si>
     <t>The Service Type list offers its 90 options with no search box, and first, middle and last all select</t>
@@ -399,7 +399,7 @@
     <t>The selector shows "Lighting"</t>
   </si>
   <si>
-    <t>TC-ISR-PGR-018</t>
+    <t>TC-ISR-APG-011</t>
   </si>
   <si>
     <t>A name already used by another group is rejected, with or without a trailing space</t>
@@ -426,7 +426,7 @@
     <t>The list page returns; nothing was created</t>
   </si>
   <si>
-    <t>TC-ISR-PGR-019</t>
+    <t>TC-ISR-APG-012</t>
   </si>
   <si>
     <t>A description already used by another group is rejected even with a new name</t>
@@ -438,7 +438,7 @@
     <t>An error toast reads `Product group name '&lt;the new name&gt;' or group description 'walk probe A' already exists.`; the page stays on the Add form; Save is still enabled</t>
   </si>
   <si>
-    <t>TC-ISR-PGR-020</t>
+    <t>TC-ISR-APG-013</t>
   </si>
   <si>
     <t>The picker search filters the catalog by substring regardless of case and empties on no match</t>
@@ -484,7 +484,7 @@
     <t>The list page returns</t>
   </si>
   <si>
-    <t>TC-ISR-PGR-021</t>
+    <t>TC-ISR-APG-014</t>
   </si>
   <si>
     <t>The Labor filter narrows the catalog and unchecking restores it</t>
@@ -508,7 +508,7 @@
     <t>The count and first row from step 1 return</t>
   </si>
   <si>
-    <t>TC-ISR-PGR-022</t>
+    <t>TC-ISR-APG-015</t>
   </si>
   <si>
     <t>Sort order flips the catalog between ascending and descending</t>
@@ -532,7 +532,7 @@
     <t>Step 1's first and last rows return</t>
   </si>
   <si>
-    <t>TC-ISR-PGR-023</t>
+    <t>TC-ISR-APG-016</t>
   </si>
   <si>
     <t>Reset clears the picker's search, filter and sort but keeps an added sub-class</t>
@@ -562,7 +562,7 @@
     <t>Search is empty, Labor is unchecked, the order shows Ascending, the full catalog is back — and the sub-class added in step 1 is still in the Sub Classes area</t>
   </si>
   <si>
-    <t>TC-ISR-PGR-024</t>
+    <t>TC-ISR-APG-017</t>
   </si>
   <si>
     <t>Double-click adds an item once and the x control removes it</t>
@@ -586,7 +586,7 @@
     <t>The Sub Classes area is empty and the instruction text is back; the catalog is unchanged</t>
   </si>
   <si>
-    <t>TC-ISR-PGR-025</t>
+    <t>TC-ISR-APG-018</t>
   </si>
   <si>
     <t>Dragging an item onto the Sub Classes area adds it</t>
@@ -604,7 +604,7 @@
     <t>2. Click Cancel</t>
   </si>
   <si>
-    <t>TC-ISR-PGR-026</t>
+    <t>TC-ISR-APG-019</t>
   </si>
   <si>
     <t>The divider button collapses and expands the sub-class panel</t>
@@ -635,7 +635,7 @@
     <t>The button reads "Collapse search panel" again and the Name box has step 1's left edge and width</t>
   </si>
   <si>
-    <t>TC-ISR-PGR-027</t>
+    <t>TC-ISR-APG-020</t>
   </si>
   <si>
     <t>A group saved with Active cleared is created inactive and found with the list's Active filter cleared</t>
@@ -662,7 +662,7 @@
     <t>5. Clear the Active filter and search again</t>
   </si>
   <si>
-    <t>TC-ISR-PGR-028</t>
+    <t>TC-ISR-APG-021</t>
   </si>
   <si>
     <t>Special characters in the name are stored verbatim and the last Service Type saves</t>
@@ -686,7 +686,7 @@
     <t>4. Search the list for the new group</t>
   </si>
   <si>
-    <t>TC-ISR-PGR-029</t>
+    <t>TC-ISR-APG-022</t>
   </si>
   <si>
     <t>Browser Back leaves the Add page without saving or warning</t>
@@ -713,7 +713,7 @@
     <t>The form is empty; nothing was kept</t>
   </si>
   <si>
-    <t>TC-ISR-PGR-030</t>
+    <t>TC-ISR-APG-023</t>
   </si>
   <si>
     <t>The breadcrumb leaves the Add page without saving or warning</t>
@@ -743,7 +743,7 @@
     <t>Pass:23 Fail:0 Skipped:0 Blocked:0</t>
   </si>
   <si>
-    <t>Last Updated: 2026-09-09</t>
+    <t>Last Updated: 2026-09-10</t>
   </si>
 </sst>
 </file>
